--- a/students/Agametov A. M/Lab3/ЛР3. ОЦЕНКА ПРОЕКТА.xlsx
+++ b/students/Agametov A. M/Lab3/ЛР3. ОЦЕНКА ПРОЕКТА.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HUAWEI\Desktop\IT-project-management-AI-23\students\Agametov A. M\Lab3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03EDC5FD-D118-46CD-A4F5-D2DDE869C5DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9F2CC8B-31EE-49BE-A0FB-5DFBED71F726}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10860" yWindow="0" windowWidth="10830" windowHeight="13770" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table 2" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="127">
   <si>
     <t xml:space="preserve"> </t>
   </si>
@@ -98,9 +98,6 @@
     <t>Экспорт отчётов в PDF</t>
   </si>
   <si>
-    <t>Реализация автосохранения данных каждые 5 минут</t>
-  </si>
-  <si>
     <t>Создание локальной резервной копии базы данных</t>
   </si>
   <si>
@@ -200,24 +197,12 @@
     <t>Настройка и конфигурирование системы</t>
   </si>
   <si>
-    <t>Передача в опытную эксплуатацию</t>
-  </si>
-  <si>
     <t>Сопровождение опытной эксплуатации</t>
   </si>
   <si>
     <t>Передача результатов работ заказчику</t>
   </si>
   <si>
-    <t>Передача исходных кодов и сопроводительной документации</t>
-  </si>
-  <si>
-    <t>Гарантийное сопровождение</t>
-  </si>
-  <si>
-    <t>Передача в промышленную эксплуатацию</t>
-  </si>
-  <si>
     <t>Формирование команды проекта</t>
   </si>
   <si>
@@ -240,9 +225,6 @@
   </si>
   <si>
     <t>Оптимальная длительность проекта (месяцы)</t>
-  </si>
-  <si>
-    <t>Реализация четырехуровневой модели</t>
   </si>
   <si>
     <t>Разработка шаблонов отчётов</t>
@@ -519,6 +501,12 @@
   <si>
     <t>Оптимист</t>
   </si>
+  <si>
+    <t>Реализация четырехуровневой пользовательской модели</t>
+  </si>
+  <si>
+    <t>Реализация автосохранения данных</t>
+  </si>
 </sst>
 </file>
 
@@ -528,7 +516,7 @@
     <numFmt numFmtId="164" formatCode="0."/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -591,6 +579,11 @@
       <name val="Times New Roman"/>
       <family val="1"/>
       <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Times New Roman"/>
     </font>
   </fonts>
   <fills count="7">
@@ -913,7 +906,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -1106,6 +1099,18 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1126,9 +1131,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1435,7 +1437,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:J97"/>
+  <dimension ref="A1:J93"/>
   <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -1449,89 +1451,89 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="30.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="67"/>
-      <c r="B1" s="67"/>
-      <c r="C1" s="67"/>
+      <c r="A1" s="71"/>
+      <c r="B1" s="71"/>
+      <c r="C1" s="71"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="62" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="G1" s="62" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
     </row>
     <row r="2" spans="1:10" ht="30.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="67"/>
-      <c r="B2" s="67"/>
-      <c r="C2" s="67"/>
+      <c r="A2" s="71"/>
+      <c r="B2" s="71"/>
+      <c r="C2" s="71"/>
       <c r="D2" s="63"/>
       <c r="E2" s="61" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="F2" s="3">
-        <f>E93/8</f>
-        <v>59.125</v>
+        <f>E89/8</f>
+        <v>15</v>
       </c>
       <c r="G2" s="3">
-        <f>E93/8</f>
-        <v>59.125</v>
+        <f>E89/8</f>
+        <v>15</v>
       </c>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
     </row>
     <row r="3" spans="1:10" ht="30.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="67"/>
-      <c r="B3" s="67"/>
-      <c r="C3" s="67"/>
-      <c r="D3" s="69" t="s">
-        <v>73</v>
-      </c>
-      <c r="E3" s="69"/>
+      <c r="A3" s="71"/>
+      <c r="B3" s="71"/>
+      <c r="C3" s="71"/>
+      <c r="D3" s="73" t="s">
+        <v>67</v>
+      </c>
+      <c r="E3" s="73"/>
       <c r="F3" s="3">
         <f>F2/22</f>
-        <v>2.6875</v>
+        <v>0.68181818181818177</v>
       </c>
       <c r="G3" s="3">
         <f>G2/22</f>
-        <v>2.6875</v>
+        <v>0.68181818181818177</v>
       </c>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
     </row>
     <row r="4" spans="1:10" ht="30.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="67"/>
-      <c r="B4" s="67"/>
-      <c r="C4" s="67"/>
-      <c r="D4" s="69" t="s">
-        <v>67</v>
-      </c>
-      <c r="E4" s="69"/>
+      <c r="A4" s="71"/>
+      <c r="B4" s="71"/>
+      <c r="C4" s="71"/>
+      <c r="D4" s="73" t="s">
+        <v>62</v>
+      </c>
+      <c r="E4" s="73"/>
       <c r="F4" s="3">
         <f>F3/4</f>
-        <v>0.671875</v>
+        <v>0.17045454545454544</v>
       </c>
       <c r="G4" s="3">
         <f>G3/4</f>
-        <v>0.671875</v>
+        <v>0.17045454545454544</v>
       </c>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
     </row>
     <row r="5" spans="1:10" ht="27.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="67"/>
-      <c r="B5" s="67"/>
-      <c r="C5" s="67"/>
-      <c r="D5" s="69" t="s">
-        <v>74</v>
-      </c>
-      <c r="E5" s="69"/>
+      <c r="A5" s="71"/>
+      <c r="B5" s="71"/>
+      <c r="C5" s="71"/>
+      <c r="D5" s="73" t="s">
+        <v>68</v>
+      </c>
+      <c r="E5" s="73"/>
       <c r="F5" s="4">
         <v>300</v>
       </c>
@@ -1543,20 +1545,20 @@
       <c r="J5" s="2"/>
     </row>
     <row r="6" spans="1:10" ht="30.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="68"/>
-      <c r="B6" s="68"/>
-      <c r="C6" s="68"/>
-      <c r="D6" s="70" t="s">
-        <v>75</v>
-      </c>
-      <c r="E6" s="70"/>
+      <c r="A6" s="72"/>
+      <c r="B6" s="72"/>
+      <c r="C6" s="72"/>
+      <c r="D6" s="74" t="s">
+        <v>69</v>
+      </c>
+      <c r="E6" s="74"/>
       <c r="F6" s="5">
-        <f>F5*H93</f>
-        <v>843300</v>
+        <f>F5*H89</f>
+        <v>214800</v>
       </c>
       <c r="G6" s="5">
-        <f>G5*H93</f>
-        <v>983850</v>
+        <f>G5*H89</f>
+        <v>250600</v>
       </c>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
@@ -1564,25 +1566,25 @@
     </row>
     <row r="7" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="E7" s="71" t="s">
-        <v>130</v>
+        <v>99</v>
+      </c>
+      <c r="E7" s="64" t="s">
+        <v>124</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="H7" s="14"/>
       <c r="J7" s="2"/>
@@ -1591,14 +1593,14 @@
       <c r="A8" s="11"/>
       <c r="B8" s="11"/>
       <c r="C8" s="12" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="E8" s="64"/>
-      <c r="F8" s="65"/>
-      <c r="G8" s="66"/>
+        <v>71</v>
+      </c>
+      <c r="E8" s="68"/>
+      <c r="F8" s="69"/>
+      <c r="G8" s="70"/>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
@@ -1623,19 +1625,19 @@
       <c r="A10" s="19"/>
       <c r="B10" s="19"/>
       <c r="C10" s="20" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="D10" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="E10" s="22">
+      <c r="E10" s="65">
+        <v>1</v>
+      </c>
+      <c r="F10" s="66">
+        <v>2</v>
+      </c>
+      <c r="G10" s="67">
         <v>4</v>
-      </c>
-      <c r="F10" s="23">
-        <v>8</v>
-      </c>
-      <c r="G10" s="24">
-        <v>16</v>
       </c>
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
@@ -1645,19 +1647,19 @@
       <c r="A11" s="25"/>
       <c r="B11" s="25"/>
       <c r="C11" s="20" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="D11" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="E11" s="22">
+      <c r="E11" s="65">
+        <v>2</v>
+      </c>
+      <c r="F11" s="66">
+        <v>4</v>
+      </c>
+      <c r="G11" s="67">
         <v>6</v>
-      </c>
-      <c r="F11" s="23">
-        <v>12</v>
-      </c>
-      <c r="G11" s="24">
-        <v>20</v>
       </c>
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
@@ -1667,19 +1669,19 @@
       <c r="A12" s="25"/>
       <c r="B12" s="25"/>
       <c r="C12" s="20" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="D12" s="21" t="s">
-        <v>68</v>
-      </c>
-      <c r="E12" s="22">
-        <v>6</v>
-      </c>
-      <c r="F12" s="23">
-        <v>12</v>
-      </c>
-      <c r="G12" s="24">
-        <v>20</v>
+        <v>125</v>
+      </c>
+      <c r="E12" s="65">
+        <v>2</v>
+      </c>
+      <c r="F12" s="66">
+        <v>4</v>
+      </c>
+      <c r="G12" s="67">
+        <v>7</v>
       </c>
       <c r="J12" s="2"/>
     </row>
@@ -1687,19 +1689,19 @@
       <c r="A13" s="25"/>
       <c r="B13" s="25"/>
       <c r="C13" s="20" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="D13" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="E13" s="22">
-        <v>4</v>
-      </c>
-      <c r="F13" s="23">
-        <v>8</v>
-      </c>
-      <c r="G13" s="24">
-        <v>16</v>
+      <c r="E13" s="65">
+        <v>1</v>
+      </c>
+      <c r="F13" s="66">
+        <v>2</v>
+      </c>
+      <c r="G13" s="67">
+        <v>3</v>
       </c>
       <c r="J13" s="2"/>
     </row>
@@ -1707,19 +1709,19 @@
       <c r="A14" s="25"/>
       <c r="B14" s="25"/>
       <c r="C14" s="20" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="D14" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="E14" s="22">
+      <c r="E14" s="65">
+        <v>1</v>
+      </c>
+      <c r="F14" s="66">
+        <v>2</v>
+      </c>
+      <c r="G14" s="67">
         <v>4</v>
-      </c>
-      <c r="F14" s="23">
-        <v>8</v>
-      </c>
-      <c r="G14" s="24">
-        <v>16</v>
       </c>
       <c r="J14" s="2"/>
     </row>
@@ -1743,19 +1745,19 @@
       <c r="A16" s="25"/>
       <c r="B16" s="25"/>
       <c r="C16" s="20" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="D16" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="E16" s="22">
-        <v>7</v>
-      </c>
-      <c r="F16" s="23">
-        <v>14</v>
-      </c>
-      <c r="G16" s="24">
-        <v>20</v>
+      <c r="E16" s="65">
+        <v>3</v>
+      </c>
+      <c r="F16" s="66">
+        <v>5</v>
+      </c>
+      <c r="G16" s="67">
+        <v>8</v>
       </c>
       <c r="J16" s="2"/>
     </row>
@@ -1763,19 +1765,19 @@
       <c r="A17" s="25"/>
       <c r="B17" s="25"/>
       <c r="C17" s="20" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="D17" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="E17" s="22">
-        <v>7</v>
-      </c>
-      <c r="F17" s="23">
-        <v>14</v>
-      </c>
-      <c r="G17" s="24">
-        <v>20</v>
+      <c r="E17" s="65">
+        <v>1</v>
+      </c>
+      <c r="F17" s="66">
+        <v>2</v>
+      </c>
+      <c r="G17" s="67">
+        <v>4</v>
       </c>
       <c r="J17" s="2"/>
     </row>
@@ -1783,19 +1785,19 @@
       <c r="A18" s="25"/>
       <c r="B18" s="25"/>
       <c r="C18" s="20" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D18" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="E18" s="22">
-        <v>7</v>
-      </c>
-      <c r="F18" s="23">
-        <v>14</v>
-      </c>
-      <c r="G18" s="24">
-        <v>20</v>
+      <c r="E18" s="65">
+        <v>2</v>
+      </c>
+      <c r="F18" s="66">
+        <v>4</v>
+      </c>
+      <c r="G18" s="67">
+        <v>6</v>
       </c>
       <c r="J18" s="2"/>
     </row>
@@ -1803,19 +1805,19 @@
       <c r="A19" s="25"/>
       <c r="B19" s="25"/>
       <c r="C19" s="20" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="D19" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="E19" s="22">
-        <v>7</v>
-      </c>
-      <c r="F19" s="23">
-        <v>14</v>
-      </c>
-      <c r="G19" s="24">
-        <v>20</v>
+      <c r="E19" s="65">
+        <v>2</v>
+      </c>
+      <c r="F19" s="66">
+        <v>4</v>
+      </c>
+      <c r="G19" s="67">
+        <v>6</v>
       </c>
       <c r="J19" s="2"/>
     </row>
@@ -1823,7 +1825,7 @@
       <c r="A20" s="15"/>
       <c r="B20" s="15"/>
       <c r="C20" s="16" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D20" s="17" t="s">
         <v>13</v>
@@ -1837,19 +1839,19 @@
       <c r="A21" s="19"/>
       <c r="B21" s="19"/>
       <c r="C21" s="20" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="D21" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="E21" s="22">
-        <v>8</v>
-      </c>
-      <c r="F21" s="23">
-        <v>16</v>
-      </c>
-      <c r="G21" s="24">
-        <v>24</v>
+      <c r="E21" s="65">
+        <v>2</v>
+      </c>
+      <c r="F21" s="66">
+        <v>4</v>
+      </c>
+      <c r="G21" s="67">
+        <v>6</v>
       </c>
       <c r="J21" s="2"/>
     </row>
@@ -1857,19 +1859,19 @@
       <c r="A22" s="25"/>
       <c r="B22" s="25"/>
       <c r="C22" s="20" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="D22" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="E22" s="22">
-        <v>8</v>
-      </c>
-      <c r="F22" s="23">
-        <v>16</v>
-      </c>
-      <c r="G22" s="24">
-        <v>24</v>
+      <c r="E22" s="65">
+        <v>1</v>
+      </c>
+      <c r="F22" s="66">
+        <v>2</v>
+      </c>
+      <c r="G22" s="67">
+        <v>4</v>
       </c>
       <c r="J22" s="2"/>
     </row>
@@ -1877,19 +1879,19 @@
       <c r="A23" s="25"/>
       <c r="B23" s="25"/>
       <c r="C23" s="20" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="D23" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="E23" s="22">
-        <v>4</v>
-      </c>
-      <c r="F23" s="23">
-        <v>8</v>
-      </c>
-      <c r="G23" s="24">
-        <v>16</v>
+      <c r="E23" s="65">
+        <v>1</v>
+      </c>
+      <c r="F23" s="66">
+        <v>2</v>
+      </c>
+      <c r="G23" s="67">
+        <v>3</v>
       </c>
       <c r="J23" s="2"/>
     </row>
@@ -1911,19 +1913,19 @@
       <c r="A25" s="25"/>
       <c r="B25" s="25"/>
       <c r="C25" s="20" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="D25" s="27" t="s">
-        <v>69</v>
-      </c>
-      <c r="E25" s="22">
-        <v>8</v>
-      </c>
-      <c r="F25" s="23">
-        <v>16</v>
-      </c>
-      <c r="G25" s="24">
-        <v>24</v>
+        <v>63</v>
+      </c>
+      <c r="E25" s="65">
+        <v>2</v>
+      </c>
+      <c r="F25" s="66">
+        <v>4</v>
+      </c>
+      <c r="G25" s="67">
+        <v>6</v>
       </c>
       <c r="J25" s="2"/>
     </row>
@@ -1931,19 +1933,19 @@
       <c r="A26" s="25"/>
       <c r="B26" s="25"/>
       <c r="C26" s="20" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D26" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="E26" s="22">
-        <v>16</v>
-      </c>
-      <c r="F26" s="23">
-        <v>24</v>
-      </c>
-      <c r="G26" s="24">
-        <v>40</v>
+      <c r="E26" s="65">
+        <v>3</v>
+      </c>
+      <c r="F26" s="66">
+        <v>5</v>
+      </c>
+      <c r="G26" s="67">
+        <v>8</v>
       </c>
       <c r="J26" s="2"/>
     </row>
@@ -1951,19 +1953,19 @@
       <c r="A27" s="25"/>
       <c r="B27" s="25"/>
       <c r="C27" s="20" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="D27" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="E27" s="22">
-        <v>8</v>
-      </c>
-      <c r="F27" s="23">
-        <v>16</v>
-      </c>
-      <c r="G27" s="24">
-        <v>24</v>
+      <c r="E27" s="65">
+        <v>2</v>
+      </c>
+      <c r="F27" s="66">
+        <v>4</v>
+      </c>
+      <c r="G27" s="67">
+        <v>6</v>
       </c>
       <c r="J27" s="2"/>
     </row>
@@ -1974,7 +1976,7 @@
         <v>1.5</v>
       </c>
       <c r="D28" s="17" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="E28" s="18"/>
       <c r="F28" s="18"/>
@@ -1985,19 +1987,19 @@
       <c r="A29" s="25"/>
       <c r="B29" s="25"/>
       <c r="C29" s="20" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="D29" s="28" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="E29" s="22">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="F29" s="23">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="G29" s="24">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="J29" s="2"/>
     </row>
@@ -2019,19 +2021,19 @@
       <c r="A31" s="19"/>
       <c r="B31" s="19"/>
       <c r="C31" s="30" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="D31" s="31" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="E31" s="32">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F31" s="33">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="G31" s="24">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="J31" s="2"/>
     </row>
@@ -2039,19 +2041,19 @@
       <c r="A32" s="25"/>
       <c r="B32" s="25"/>
       <c r="C32" s="20" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="D32" s="28" t="s">
         <v>19</v>
       </c>
       <c r="E32" s="22">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F32" s="23">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="G32" s="24">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="J32" s="2"/>
     </row>
@@ -2062,7 +2064,7 @@
         <v>1.7</v>
       </c>
       <c r="D33" s="17" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E33" s="18"/>
       <c r="F33" s="18"/>
@@ -2073,19 +2075,19 @@
       <c r="A34" s="25"/>
       <c r="B34" s="25"/>
       <c r="C34" s="20" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="D34" s="27" t="s">
-        <v>20</v>
+        <v>126</v>
       </c>
       <c r="E34" s="22">
+        <v>2</v>
+      </c>
+      <c r="F34" s="23">
         <v>4</v>
       </c>
-      <c r="F34" s="23">
-        <v>8</v>
-      </c>
       <c r="G34" s="24">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="J34" s="2"/>
     </row>
@@ -2093,19 +2095,19 @@
       <c r="A35" s="25"/>
       <c r="B35" s="25"/>
       <c r="C35" s="20" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="D35" s="27" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E35" s="22">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F35" s="23">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="G35" s="24">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="J35" s="2"/>
     </row>
@@ -2116,7 +2118,7 @@
         <v>1.8</v>
       </c>
       <c r="D36" s="17" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E36" s="18"/>
       <c r="F36" s="18"/>
@@ -2127,19 +2129,19 @@
       <c r="A37" s="25"/>
       <c r="B37" s="25"/>
       <c r="C37" s="20" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D37" s="27" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E37" s="22">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F37" s="23">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="G37" s="24">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="J37" s="2"/>
     </row>
@@ -2147,19 +2149,19 @@
       <c r="A38" s="25"/>
       <c r="B38" s="25"/>
       <c r="C38" s="20" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D38" s="27" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E38" s="22">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F38" s="23">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G38" s="24">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="J38" s="2"/>
     </row>
@@ -2170,7 +2172,7 @@
         <v>1.9</v>
       </c>
       <c r="D39" s="17" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E39" s="18"/>
       <c r="F39" s="18"/>
@@ -2181,19 +2183,19 @@
       <c r="A40" s="25"/>
       <c r="B40" s="25"/>
       <c r="C40" s="20" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D40" s="27" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E40" s="22">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F40" s="23">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="G40" s="24">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="J40" s="2"/>
     </row>
@@ -2201,19 +2203,19 @@
       <c r="A41" s="25"/>
       <c r="B41" s="25"/>
       <c r="C41" s="20" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="D41" s="27" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E41" s="22">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F41" s="23">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="G41" s="24">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="J41" s="2"/>
     </row>
@@ -2221,10 +2223,10 @@
       <c r="A42" s="26"/>
       <c r="B42" s="26"/>
       <c r="C42" s="16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D42" s="17" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="E42" s="18"/>
       <c r="F42" s="18"/>
@@ -2235,19 +2237,19 @@
       <c r="A43" s="25"/>
       <c r="B43" s="25"/>
       <c r="C43" s="20" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D43" s="27" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E43" s="22">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F43" s="23">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="G43" s="24">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="J43" s="2"/>
     </row>
@@ -2255,19 +2257,19 @@
       <c r="A44" s="25"/>
       <c r="B44" s="25"/>
       <c r="C44" s="20" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="D44" s="27" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E44" s="22">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F44" s="23">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="G44" s="24">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="J44" s="2"/>
     </row>
@@ -2275,10 +2277,10 @@
       <c r="A45" s="26"/>
       <c r="B45" s="26"/>
       <c r="C45" s="16" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D45" s="17" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="E45" s="18"/>
       <c r="F45" s="18"/>
@@ -2289,19 +2291,19 @@
       <c r="A46" s="25"/>
       <c r="B46" s="25"/>
       <c r="C46" s="20" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D46" s="27" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E46" s="22">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="F46" s="23">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="G46" s="24">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="J46" s="2"/>
     </row>
@@ -2309,19 +2311,19 @@
       <c r="A47" s="25"/>
       <c r="B47" s="25"/>
       <c r="C47" s="20" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="D47" s="27" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E47" s="22">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F47" s="23">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="G47" s="24">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="J47" s="2"/>
     </row>
@@ -2329,10 +2331,10 @@
       <c r="A48" s="26"/>
       <c r="B48" s="26"/>
       <c r="C48" s="16" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D48" s="17" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="E48" s="18"/>
       <c r="F48" s="18"/>
@@ -2343,19 +2345,19 @@
       <c r="A49" s="25"/>
       <c r="B49" s="25"/>
       <c r="C49" s="20" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D49" s="27" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="E49" s="22">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F49" s="23">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="G49" s="24">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="J49" s="2"/>
     </row>
@@ -2363,19 +2365,19 @@
       <c r="A50" s="25"/>
       <c r="B50" s="25"/>
       <c r="C50" s="20" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="D50" s="27" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E50" s="22">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F50" s="23">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="G50" s="24">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="J50" s="2"/>
     </row>
@@ -2395,10 +2397,10 @@
         <v>2</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D52" s="40" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E52" s="41"/>
       <c r="F52" s="42"/>
@@ -2412,16 +2414,16 @@
         <v>2.1</v>
       </c>
       <c r="D53" s="27" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="E53" s="22">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="F53" s="23">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="G53" s="24">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="J53" s="2"/>
     </row>
@@ -2432,16 +2434,16 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="D54" s="27" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E54" s="22">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="F54" s="23">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="G54" s="24">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="J54" s="2"/>
     </row>
@@ -2452,16 +2454,16 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="D55" s="27" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="E55" s="22">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F55" s="23">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="G55" s="24">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="J55" s="2"/>
     </row>
@@ -2472,16 +2474,16 @@
         <v>2.4</v>
       </c>
       <c r="D56" s="27" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E56" s="22">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F56" s="23">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="G56" s="24">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="J56" s="2"/>
     </row>
@@ -2492,16 +2494,16 @@
         <v>2.5</v>
       </c>
       <c r="D57" s="27" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="E57" s="22">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F57" s="23">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="G57" s="24">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="J57" s="2"/>
     </row>
@@ -2522,7 +2524,7 @@
         <v>3</v>
       </c>
       <c r="D59" s="40" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="E59" s="41"/>
       <c r="F59" s="42"/>
@@ -2536,16 +2538,16 @@
         <v>3.1</v>
       </c>
       <c r="D60" s="27" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="E60" s="22">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="F60" s="23">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="G60" s="24">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="J60" s="2"/>
     </row>
@@ -2556,16 +2558,16 @@
         <v>3.2</v>
       </c>
       <c r="D61" s="27" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="E61" s="22">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F61" s="23">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="G61" s="24">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="J61" s="2"/>
     </row>
@@ -2576,16 +2578,16 @@
         <v>3.3</v>
       </c>
       <c r="D62" s="27" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="E62" s="22">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F62" s="23">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="G62" s="24">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="J62" s="2"/>
     </row>
@@ -2596,16 +2598,16 @@
         <v>3.4</v>
       </c>
       <c r="D63" s="27" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="E63" s="22">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F63" s="23">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="G63" s="24">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="J63" s="2"/>
     </row>
@@ -2626,7 +2628,7 @@
         <v>4</v>
       </c>
       <c r="D65" s="40" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="E65" s="46"/>
       <c r="F65" s="47"/>
@@ -2640,16 +2642,16 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="D66" s="27" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E66" s="22">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F66" s="23">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G66" s="49">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="J66" s="2"/>
     </row>
@@ -2660,16 +2662,16 @@
         <v>4.2</v>
       </c>
       <c r="D67" s="27" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E67" s="22">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F67" s="23">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G67" s="49">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="J67" s="2"/>
     </row>
@@ -2680,16 +2682,16 @@
         <v>4.3</v>
       </c>
       <c r="D68" s="27" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E68" s="22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F68" s="23">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G68" s="49">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J68" s="2"/>
     </row>
@@ -2710,7 +2712,7 @@
         <v>5</v>
       </c>
       <c r="D70" s="40" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="E70" s="41"/>
       <c r="F70" s="42"/>
@@ -2724,16 +2726,16 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="D71" s="27" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E71" s="22">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F71" s="23">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G71" s="24">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="J71" s="2"/>
     </row>
@@ -2744,116 +2746,100 @@
         <v>5.2</v>
       </c>
       <c r="D72" s="27" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E72" s="22">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F72" s="23">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G72" s="24">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="J72" s="2"/>
     </row>
     <row r="73" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="19"/>
       <c r="B73" s="19"/>
-      <c r="C73" s="44">
+      <c r="C73" s="52">
         <v>5.3</v>
       </c>
-      <c r="D73" s="27" t="s">
-        <v>54</v>
-      </c>
-      <c r="E73" s="22">
-        <v>4</v>
-      </c>
-      <c r="F73" s="23">
-        <v>6</v>
-      </c>
-      <c r="G73" s="24">
-        <v>12</v>
+      <c r="D73" s="31" t="s">
+        <v>53</v>
+      </c>
+      <c r="E73" s="32">
+        <v>2</v>
+      </c>
+      <c r="F73" s="33">
+        <v>3</v>
+      </c>
+      <c r="G73" s="53">
+        <v>5</v>
       </c>
       <c r="J73" s="2"/>
     </row>
     <row r="74" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="19"/>
       <c r="B74" s="19"/>
-      <c r="C74" s="52">
+      <c r="C74" s="44">
         <v>5.4</v>
       </c>
-      <c r="D74" s="31" t="s">
-        <v>55</v>
-      </c>
-      <c r="E74" s="32">
-        <v>8</v>
-      </c>
-      <c r="F74" s="33">
-        <v>16</v>
-      </c>
-      <c r="G74" s="53">
-        <v>24</v>
+      <c r="D74" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="E74" s="22">
+        <v>1</v>
+      </c>
+      <c r="F74" s="23">
+        <v>2</v>
+      </c>
+      <c r="G74" s="24">
+        <v>3</v>
       </c>
       <c r="J74" s="2"/>
     </row>
-    <row r="75" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="19"/>
-      <c r="B75" s="19"/>
-      <c r="C75" s="44">
-        <v>5.5</v>
-      </c>
-      <c r="D75" s="27" t="s">
-        <v>56</v>
-      </c>
-      <c r="E75" s="22">
-        <v>2</v>
-      </c>
-      <c r="F75" s="23">
-        <v>3</v>
-      </c>
-      <c r="G75" s="24">
-        <v>8</v>
-      </c>
+      <c r="B75" s="50"/>
+      <c r="C75" s="51"/>
+      <c r="D75" s="28"/>
+      <c r="E75" s="36"/>
+      <c r="F75" s="37"/>
+      <c r="G75" s="38"/>
       <c r="J75" s="2"/>
     </row>
-    <row r="76" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="25"/>
-      <c r="B76" s="25"/>
-      <c r="C76" s="44">
-        <v>5.6</v>
-      </c>
-      <c r="D76" s="28" t="s">
-        <v>57</v>
-      </c>
-      <c r="E76" s="22">
-        <v>4</v>
-      </c>
-      <c r="F76" s="23">
-        <v>8</v>
-      </c>
-      <c r="G76" s="24">
-        <v>12</v>
-      </c>
+    <row r="76" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A76" s="11"/>
+      <c r="B76" s="54"/>
+      <c r="C76" s="55">
+        <v>6</v>
+      </c>
+      <c r="D76" s="56" t="s">
+        <v>94</v>
+      </c>
+      <c r="E76" s="41"/>
+      <c r="F76" s="42"/>
+      <c r="G76" s="43"/>
       <c r="J76" s="2"/>
     </row>
     <row r="77" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="19"/>
       <c r="B77" s="19"/>
       <c r="C77" s="44">
-        <v>5.7</v>
+        <v>6.1</v>
       </c>
       <c r="D77" s="27" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E77" s="22">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F77" s="23">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G77" s="24">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="J77" s="2"/>
     </row>
@@ -2861,114 +2847,114 @@
       <c r="A78" s="19"/>
       <c r="B78" s="19"/>
       <c r="C78" s="44">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="D78" s="27" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E78" s="22">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F78" s="23">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G78" s="24">
         <v>12</v>
       </c>
       <c r="J78" s="2"/>
     </row>
-    <row r="79" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="19"/>
-      <c r="B79" s="50"/>
-      <c r="C79" s="51"/>
-      <c r="D79" s="28"/>
-      <c r="E79" s="36"/>
-      <c r="F79" s="37"/>
-      <c r="G79" s="38"/>
+      <c r="B79" s="19"/>
+      <c r="C79" s="44">
+        <v>6.3</v>
+      </c>
+      <c r="D79" s="27" t="s">
+        <v>57</v>
+      </c>
+      <c r="E79" s="22">
+        <v>1</v>
+      </c>
+      <c r="F79" s="23">
+        <v>2</v>
+      </c>
+      <c r="G79" s="24">
+        <v>4</v>
+      </c>
       <c r="J79" s="2"/>
     </row>
     <row r="80" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="11"/>
-      <c r="B80" s="54"/>
-      <c r="C80" s="55">
-        <v>6</v>
-      </c>
-      <c r="D80" s="56" t="s">
-        <v>100</v>
-      </c>
-      <c r="E80" s="41"/>
-      <c r="F80" s="42"/>
-      <c r="G80" s="43"/>
+      <c r="A80" s="19"/>
+      <c r="B80" s="19"/>
+      <c r="C80" s="44">
+        <v>6.4</v>
+      </c>
+      <c r="D80" s="27" t="s">
+        <v>58</v>
+      </c>
+      <c r="E80" s="22">
+        <v>1</v>
+      </c>
+      <c r="F80" s="23">
+        <v>2</v>
+      </c>
+      <c r="G80" s="24">
+        <v>3</v>
+      </c>
       <c r="J80" s="2"/>
     </row>
     <row r="81" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="19"/>
       <c r="B81" s="19"/>
       <c r="C81" s="44">
-        <v>6.1</v>
+        <v>6.5</v>
       </c>
       <c r="D81" s="27" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E81" s="22">
+        <v>2</v>
+      </c>
+      <c r="F81" s="23">
         <v>4</v>
       </c>
-      <c r="F81" s="23">
-        <v>8</v>
-      </c>
       <c r="G81" s="24">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J81" s="2"/>
     </row>
-    <row r="82" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A82" s="19"/>
-      <c r="B82" s="19"/>
-      <c r="C82" s="44">
-        <v>6.2</v>
-      </c>
-      <c r="D82" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="E82" s="22">
-        <v>24</v>
-      </c>
-      <c r="F82" s="23">
-        <v>40</v>
-      </c>
-      <c r="G82" s="24">
-        <v>64</v>
-      </c>
+    <row r="82" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A82" s="50"/>
+      <c r="B82" s="50"/>
+      <c r="C82" s="51"/>
+      <c r="D82" s="28"/>
+      <c r="E82" s="36"/>
+      <c r="F82" s="37"/>
+      <c r="G82" s="38"/>
       <c r="J82" s="2"/>
     </row>
     <row r="83" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A83" s="19"/>
-      <c r="B83" s="19"/>
-      <c r="C83" s="44">
-        <v>6.3</v>
-      </c>
-      <c r="D83" s="27" t="s">
-        <v>62</v>
-      </c>
-      <c r="E83" s="22">
-        <v>16</v>
-      </c>
-      <c r="F83" s="23">
-        <v>24</v>
-      </c>
-      <c r="G83" s="24">
-        <v>40</v>
-      </c>
+      <c r="A83" s="57"/>
+      <c r="B83" s="58"/>
+      <c r="C83" s="55">
+        <v>7</v>
+      </c>
+      <c r="D83" s="56" t="s">
+        <v>95</v>
+      </c>
+      <c r="E83" s="41"/>
+      <c r="F83" s="42"/>
+      <c r="G83" s="43"/>
       <c r="J83" s="2"/>
     </row>
     <row r="84" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="19"/>
       <c r="B84" s="19"/>
       <c r="C84" s="44">
-        <v>6.4</v>
+        <v>7.1</v>
       </c>
       <c r="D84" s="27" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E84" s="22">
         <v>8</v>
@@ -2981,207 +2967,143 @@
       </c>
       <c r="J84" s="2"/>
     </row>
-    <row r="85" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="19"/>
-      <c r="B85" s="19"/>
+    <row r="85" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="25"/>
+      <c r="B85" s="25"/>
       <c r="C85" s="44">
-        <v>6.5</v>
+        <v>7.2</v>
       </c>
       <c r="D85" s="27" t="s">
-        <v>64</v>
+        <v>112</v>
       </c>
       <c r="E85" s="22">
+        <v>8</v>
+      </c>
+      <c r="F85" s="23">
         <v>16</v>
       </c>
-      <c r="F85" s="23">
-        <v>32</v>
-      </c>
       <c r="G85" s="24">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="J85" s="2"/>
     </row>
-    <row r="86" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="50"/>
-      <c r="B86" s="50"/>
-      <c r="C86" s="51"/>
-      <c r="D86" s="28"/>
-      <c r="E86" s="36"/>
-      <c r="F86" s="37"/>
-      <c r="G86" s="38"/>
+    <row r="86" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A86" s="19"/>
+      <c r="B86" s="19"/>
+      <c r="C86" s="44">
+        <v>7.3</v>
+      </c>
+      <c r="D86" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="E86" s="22">
+        <v>8</v>
+      </c>
+      <c r="F86" s="23">
+        <v>16</v>
+      </c>
+      <c r="G86" s="24">
+        <v>24</v>
+      </c>
       <c r="J86" s="2"/>
     </row>
     <row r="87" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="57"/>
-      <c r="B87" s="58"/>
-      <c r="C87" s="55">
-        <v>7</v>
-      </c>
-      <c r="D87" s="56" t="s">
-        <v>101</v>
-      </c>
-      <c r="E87" s="41"/>
-      <c r="F87" s="42"/>
-      <c r="G87" s="43"/>
+      <c r="A87" s="19"/>
+      <c r="B87" s="19"/>
+      <c r="C87" s="44">
+        <v>7.4</v>
+      </c>
+      <c r="D87" s="27" t="s">
+        <v>111</v>
+      </c>
+      <c r="E87" s="22">
+        <v>8</v>
+      </c>
+      <c r="F87" s="23">
+        <v>16</v>
+      </c>
+      <c r="G87" s="24">
+        <v>24</v>
+      </c>
       <c r="J87" s="2"/>
     </row>
     <row r="88" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="19"/>
       <c r="B88" s="19"/>
-      <c r="C88" s="44">
-        <v>7.1</v>
-      </c>
-      <c r="D88" s="27" t="s">
-        <v>65</v>
-      </c>
-      <c r="E88" s="22">
-        <v>8</v>
-      </c>
-      <c r="F88" s="23">
-        <v>16</v>
-      </c>
-      <c r="G88" s="24">
-        <v>24</v>
+      <c r="C88" s="51"/>
+      <c r="D88" s="28"/>
+      <c r="E88" s="36"/>
+      <c r="F88" s="37"/>
+      <c r="G88" s="38"/>
+      <c r="H88" s="64" t="s">
+        <v>123</v>
       </c>
       <c r="J88" s="2"/>
     </row>
-    <row r="89" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="25"/>
-      <c r="B89" s="25"/>
-      <c r="C89" s="44">
-        <v>7.2</v>
-      </c>
-      <c r="D89" s="27" t="s">
-        <v>118</v>
-      </c>
-      <c r="E89" s="22">
-        <v>8</v>
-      </c>
-      <c r="F89" s="23">
-        <v>16</v>
-      </c>
-      <c r="G89" s="24">
-        <v>24</v>
+    <row r="89" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A89" s="59" t="s">
+        <v>96</v>
+      </c>
+      <c r="B89" s="19"/>
+      <c r="C89" s="51"/>
+      <c r="D89" s="37"/>
+      <c r="E89" s="60">
+        <f>SUM(E10:E87)</f>
+        <v>120</v>
+      </c>
+      <c r="F89" s="60">
+        <f t="shared" ref="F89:G89" si="0">SUM(F10:F87)</f>
+        <v>230</v>
+      </c>
+      <c r="G89" s="60">
+        <f t="shared" si="0"/>
+        <v>366</v>
+      </c>
+      <c r="H89" s="60">
+        <f>SUM(E89:G89)</f>
+        <v>716</v>
       </c>
       <c r="J89" s="2"/>
     </row>
-    <row r="90" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A90" s="19"/>
-      <c r="B90" s="19"/>
-      <c r="C90" s="44">
-        <v>7.3</v>
-      </c>
-      <c r="D90" s="27" t="s">
-        <v>66</v>
-      </c>
-      <c r="E90" s="22">
-        <v>8</v>
-      </c>
-      <c r="F90" s="23">
-        <v>16</v>
-      </c>
-      <c r="G90" s="24">
-        <v>24</v>
-      </c>
+    <row r="90" spans="1:10" ht="15.5" x14ac:dyDescent="0.3">
+      <c r="A90" s="2"/>
+      <c r="B90" s="2"/>
+      <c r="C90" s="2"/>
+      <c r="D90" s="2"/>
+      <c r="E90" s="2"/>
+      <c r="F90" s="2"/>
+      <c r="G90" s="2"/>
       <c r="J90" s="2"/>
     </row>
-    <row r="91" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A91" s="19"/>
-      <c r="B91" s="19"/>
-      <c r="C91" s="44">
-        <v>7.4</v>
-      </c>
-      <c r="D91" s="27" t="s">
-        <v>117</v>
-      </c>
-      <c r="E91" s="22">
-        <v>8</v>
-      </c>
-      <c r="F91" s="23">
-        <v>16</v>
-      </c>
-      <c r="G91" s="24">
-        <v>24</v>
-      </c>
+    <row r="91" spans="1:10" ht="15.5" x14ac:dyDescent="0.3">
+      <c r="A91" s="2"/>
+      <c r="B91" s="2"/>
+      <c r="C91" s="2"/>
+      <c r="D91" s="2"/>
+      <c r="E91" s="2"/>
+      <c r="F91" s="2"/>
+      <c r="G91" s="2"/>
       <c r="J91" s="2"/>
     </row>
-    <row r="92" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="19"/>
-      <c r="B92" s="19"/>
-      <c r="C92" s="51"/>
-      <c r="D92" s="28"/>
-      <c r="E92" s="36"/>
-      <c r="F92" s="37"/>
-      <c r="G92" s="38"/>
-      <c r="H92" s="71" t="s">
-        <v>129</v>
-      </c>
+    <row r="92" spans="1:10" ht="15.5" x14ac:dyDescent="0.3">
+      <c r="A92" s="2"/>
+      <c r="B92" s="2"/>
+      <c r="C92" s="2"/>
+      <c r="D92" s="2"/>
+      <c r="E92" s="2"/>
+      <c r="F92" s="2"/>
+      <c r="G92" s="2"/>
       <c r="J92" s="2"/>
     </row>
-    <row r="93" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="59" t="s">
-        <v>102</v>
-      </c>
-      <c r="B93" s="19"/>
-      <c r="C93" s="51"/>
-      <c r="D93" s="37"/>
-      <c r="E93" s="60">
-        <f>SUM(E10:E91)</f>
-        <v>473</v>
-      </c>
-      <c r="F93" s="60">
-        <f t="shared" ref="F93:G93" si="0">SUM(F10:F91)</f>
-        <v>898</v>
-      </c>
-      <c r="G93" s="60">
-        <f t="shared" si="0"/>
-        <v>1440</v>
-      </c>
-      <c r="H93" s="60">
-        <f>SUM(E93:G93)</f>
-        <v>2811</v>
-      </c>
+    <row r="93" spans="1:10" ht="15.5" x14ac:dyDescent="0.3">
+      <c r="A93" s="2"/>
+      <c r="B93" s="2"/>
+      <c r="C93" s="2"/>
+      <c r="D93" s="2"/>
+      <c r="E93" s="2"/>
+      <c r="F93" s="2"/>
+      <c r="G93" s="2"/>
       <c r="J93" s="2"/>
-    </row>
-    <row r="94" spans="1:10" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A94" s="2"/>
-      <c r="B94" s="2"/>
-      <c r="C94" s="2"/>
-      <c r="D94" s="2"/>
-      <c r="E94" s="2"/>
-      <c r="F94" s="2"/>
-      <c r="G94" s="2"/>
-      <c r="J94" s="2"/>
-    </row>
-    <row r="95" spans="1:10" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A95" s="2"/>
-      <c r="B95" s="2"/>
-      <c r="C95" s="2"/>
-      <c r="D95" s="2"/>
-      <c r="E95" s="2"/>
-      <c r="F95" s="2"/>
-      <c r="G95" s="2"/>
-      <c r="J95" s="2"/>
-    </row>
-    <row r="96" spans="1:10" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A96" s="2"/>
-      <c r="B96" s="2"/>
-      <c r="C96" s="2"/>
-      <c r="D96" s="2"/>
-      <c r="E96" s="2"/>
-      <c r="F96" s="2"/>
-      <c r="G96" s="2"/>
-      <c r="J96" s="2"/>
-    </row>
-    <row r="97" spans="1:10" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A97" s="2"/>
-      <c r="B97" s="2"/>
-      <c r="C97" s="2"/>
-      <c r="D97" s="2"/>
-      <c r="E97" s="2"/>
-      <c r="F97" s="2"/>
-      <c r="G97" s="2"/>
-      <c r="J97" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="6">

--- a/students/Agametov A. M/Lab3/ЛР3. ОЦЕНКА ПРОЕКТА.xlsx
+++ b/students/Agametov A. M/Lab3/ЛР3. ОЦЕНКА ПРОЕКТА.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HUAWEI\Desktop\IT-project-management-AI-23\students\Agametov A. M\Lab3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2C03CDA-15E5-471C-A376-828578B87247}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A973E0FF-4FF0-480C-B2EA-46408DC2DB8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10710" yWindow="0" windowWidth="10980" windowHeight="13770" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table 2" sheetId="2" r:id="rId1"/>
@@ -1185,6 +1185,75 @@
     <xf numFmtId="49" fontId="8" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="1" fontId="10" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="10" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="10" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="10" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1196,75 +1265,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="10" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="10" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="10" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="10" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1585,9 +1585,9 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="30.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="55"/>
-      <c r="B1" s="55"/>
-      <c r="C1" s="55"/>
+      <c r="A1" s="78"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="42" t="s">
@@ -1601,93 +1601,93 @@
       <c r="J1" s="2"/>
     </row>
     <row r="2" spans="1:10" ht="30.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="55"/>
-      <c r="B2" s="55"/>
-      <c r="C2" s="55"/>
+      <c r="A2" s="78"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
       <c r="D2" s="43"/>
       <c r="E2" s="41" t="s">
         <v>117</v>
       </c>
       <c r="F2" s="3">
         <f>E90</f>
-        <v>293</v>
+        <v>2051</v>
       </c>
       <c r="G2" s="3">
         <f>G90</f>
-        <v>1321</v>
+        <v>11889</v>
       </c>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
     </row>
     <row r="3" spans="1:10" ht="30.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="55"/>
-      <c r="B3" s="55"/>
-      <c r="C3" s="55"/>
-      <c r="D3" s="57" t="s">
+      <c r="A3" s="78"/>
+      <c r="B3" s="78"/>
+      <c r="C3" s="78"/>
+      <c r="D3" s="80" t="s">
         <v>123</v>
       </c>
-      <c r="E3" s="57"/>
+      <c r="E3" s="80"/>
       <c r="F3" s="3">
         <f>F2/8</f>
-        <v>36.625</v>
+        <v>256.375</v>
       </c>
       <c r="G3" s="3">
         <f>G2/8</f>
-        <v>165.125</v>
+        <v>1486.125</v>
       </c>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
     </row>
     <row r="4" spans="1:10" ht="30.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="55"/>
-      <c r="B4" s="55"/>
-      <c r="C4" s="55"/>
-      <c r="D4" s="57" t="s">
+      <c r="A4" s="78"/>
+      <c r="B4" s="78"/>
+      <c r="C4" s="78"/>
+      <c r="D4" s="80" t="s">
         <v>62</v>
       </c>
-      <c r="E4" s="57"/>
+      <c r="E4" s="80"/>
       <c r="F4" s="3">
         <f>F3/22</f>
-        <v>1.6647727272727273</v>
+        <v>11.653409090909092</v>
       </c>
       <c r="G4" s="3">
         <f>G3/22</f>
-        <v>7.5056818181818183</v>
+        <v>67.55113636363636</v>
       </c>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
     </row>
     <row r="5" spans="1:10" ht="27.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="55"/>
-      <c r="B5" s="55"/>
-      <c r="C5" s="55"/>
-      <c r="D5" s="57" t="s">
+      <c r="A5" s="78"/>
+      <c r="B5" s="78"/>
+      <c r="C5" s="78"/>
+      <c r="D5" s="80" t="s">
         <v>58</v>
       </c>
-      <c r="E5" s="57"/>
+      <c r="E5" s="80"/>
       <c r="F5" s="3">
         <f>F4/2</f>
-        <v>0.83238636363636365</v>
+        <v>5.8267045454545459</v>
       </c>
       <c r="G5" s="3">
         <f>G4/2</f>
-        <v>3.7528409090909092</v>
+        <v>33.77556818181818</v>
       </c>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
     </row>
     <row r="6" spans="1:10" ht="30.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="56"/>
-      <c r="B6" s="56"/>
-      <c r="C6" s="56"/>
-      <c r="D6" s="57" t="s">
+      <c r="A6" s="79"/>
+      <c r="B6" s="79"/>
+      <c r="C6" s="79"/>
+      <c r="D6" s="80" t="s">
         <v>63</v>
       </c>
-      <c r="E6" s="57"/>
+      <c r="E6" s="80"/>
       <c r="F6" s="4">
         <v>300</v>
       </c>
@@ -1699,23 +1699,23 @@
       <c r="J6" s="2"/>
     </row>
     <row r="7" spans="1:10" ht="30.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D7" s="58" t="s">
+      <c r="D7" s="81" t="s">
         <v>64</v>
       </c>
-      <c r="E7" s="58"/>
+      <c r="E7" s="81"/>
       <c r="F7" s="5">
         <f>F6*H90</f>
-        <v>179099.99999999997</v>
+        <v>1485000</v>
       </c>
       <c r="G7" s="5">
         <f>G6*H90</f>
-        <v>208949.99999999997</v>
+        <v>1732500</v>
       </c>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
     </row>
-    <row r="8" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" ht="41.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
         <v>92</v>
       </c>
@@ -1784,18 +1784,18 @@
       <c r="D11" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="E11" s="59">
-        <v>4</v>
-      </c>
-      <c r="F11" s="60">
-        <v>7</v>
-      </c>
-      <c r="G11" s="61">
-        <v>18</v>
+      <c r="E11" s="55">
+        <v>28</v>
+      </c>
+      <c r="F11" s="56">
+        <v>56</v>
+      </c>
+      <c r="G11" s="57">
+        <v>162</v>
       </c>
       <c r="H11" s="47">
         <f>(E11 + 4*F11 + G11)/6</f>
-        <v>8.3333333333333339</v>
+        <v>69</v>
       </c>
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
@@ -1809,18 +1809,18 @@
       <c r="D12" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="E12" s="59">
-        <v>6</v>
-      </c>
-      <c r="F12" s="60">
-        <v>10</v>
-      </c>
-      <c r="G12" s="61">
-        <v>27</v>
+      <c r="E12" s="55">
+        <v>42</v>
+      </c>
+      <c r="F12" s="56">
+        <v>80</v>
+      </c>
+      <c r="G12" s="57">
+        <v>243</v>
       </c>
       <c r="H12" s="47">
         <f>(E12 + 4*F12 + G12)/6</f>
-        <v>12.166666666666666</v>
+        <v>100.83333333333333</v>
       </c>
       <c r="J12" s="2"/>
     </row>
@@ -1833,18 +1833,18 @@
       <c r="D13" s="18" t="s">
         <v>115</v>
       </c>
-      <c r="E13" s="59">
-        <v>8</v>
-      </c>
-      <c r="F13" s="60">
-        <v>14</v>
-      </c>
-      <c r="G13" s="61">
-        <v>36</v>
+      <c r="E13" s="55">
+        <v>56</v>
+      </c>
+      <c r="F13" s="56">
+        <v>112</v>
+      </c>
+      <c r="G13" s="57">
+        <v>324</v>
       </c>
       <c r="H13" s="47">
         <f t="shared" ref="H13:H75" si="0">(E13 + 4*F13 + G13)/6</f>
-        <v>16.666666666666668</v>
+        <v>138</v>
       </c>
       <c r="J13" s="2"/>
     </row>
@@ -1857,18 +1857,18 @@
       <c r="D14" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="59">
-        <v>2</v>
-      </c>
-      <c r="F14" s="60">
-        <v>3</v>
-      </c>
-      <c r="G14" s="61">
-        <v>9</v>
+      <c r="E14" s="55">
+        <v>14</v>
+      </c>
+      <c r="F14" s="56">
+        <v>24</v>
+      </c>
+      <c r="G14" s="57">
+        <v>81</v>
       </c>
       <c r="H14" s="47">
         <f>(E14 + 4*F14 + G14)/6</f>
-        <v>3.8333333333333335</v>
+        <v>31.833333333333332</v>
       </c>
       <c r="J14" s="2"/>
     </row>
@@ -1881,18 +1881,18 @@
       <c r="D15" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="E15" s="59">
-        <v>3</v>
-      </c>
-      <c r="F15" s="60">
-        <v>5</v>
-      </c>
-      <c r="G15" s="61">
-        <v>14</v>
+      <c r="E15" s="55">
+        <v>21</v>
+      </c>
+      <c r="F15" s="56">
+        <v>40</v>
+      </c>
+      <c r="G15" s="57">
+        <v>126</v>
       </c>
       <c r="H15" s="47">
         <f>(E15 + 4*F15 + G15)/6</f>
-        <v>6.166666666666667</v>
+        <v>51.166666666666664</v>
       </c>
       <c r="J15" s="2"/>
     </row>
@@ -1922,18 +1922,18 @@
       <c r="D17" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="E17" s="66">
-        <v>8</v>
-      </c>
-      <c r="F17" s="67">
-        <v>14</v>
-      </c>
-      <c r="G17" s="68">
-        <v>36</v>
+      <c r="E17" s="62">
+        <v>56</v>
+      </c>
+      <c r="F17" s="63">
+        <v>112</v>
+      </c>
+      <c r="G17" s="64">
+        <v>324</v>
       </c>
       <c r="H17" s="47">
         <f>(E17 + 4*F17 + G17)/6</f>
-        <v>16.666666666666668</v>
+        <v>138</v>
       </c>
       <c r="J17" s="2"/>
     </row>
@@ -1946,18 +1946,18 @@
       <c r="D18" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="E18" s="66">
-        <v>3</v>
-      </c>
-      <c r="F18" s="67">
-        <v>5</v>
-      </c>
-      <c r="G18" s="68">
-        <v>14</v>
+      <c r="E18" s="62">
+        <v>21</v>
+      </c>
+      <c r="F18" s="63">
+        <v>40</v>
+      </c>
+      <c r="G18" s="64">
+        <v>126</v>
       </c>
       <c r="H18" s="47">
         <f>(E18 + 4*F18 + G18)/6</f>
-        <v>6.166666666666667</v>
+        <v>51.166666666666664</v>
       </c>
       <c r="J18" s="2"/>
     </row>
@@ -1970,18 +1970,18 @@
       <c r="D19" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="E19" s="66">
-        <v>6</v>
-      </c>
-      <c r="F19" s="67">
-        <v>10</v>
-      </c>
-      <c r="G19" s="68">
-        <v>27</v>
+      <c r="E19" s="62">
+        <v>42</v>
+      </c>
+      <c r="F19" s="63">
+        <v>80</v>
+      </c>
+      <c r="G19" s="64">
+        <v>243</v>
       </c>
       <c r="H19" s="47">
         <f t="shared" si="0"/>
-        <v>12.166666666666666</v>
+        <v>100.83333333333333</v>
       </c>
       <c r="J19" s="2"/>
     </row>
@@ -1994,18 +1994,18 @@
       <c r="D20" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="E20" s="66">
-        <v>6</v>
-      </c>
-      <c r="F20" s="67">
-        <v>10</v>
-      </c>
-      <c r="G20" s="68">
-        <v>27</v>
+      <c r="E20" s="62">
+        <v>42</v>
+      </c>
+      <c r="F20" s="63">
+        <v>80</v>
+      </c>
+      <c r="G20" s="64">
+        <v>243</v>
       </c>
       <c r="H20" s="47">
         <f t="shared" si="0"/>
-        <v>12.166666666666666</v>
+        <v>100.83333333333333</v>
       </c>
       <c r="J20" s="2"/>
     </row>
@@ -2018,9 +2018,9 @@
       <c r="D21" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="E21" s="65"/>
-      <c r="F21" s="65"/>
-      <c r="G21" s="65"/>
+      <c r="E21" s="61"/>
+      <c r="F21" s="61"/>
+      <c r="G21" s="61"/>
       <c r="H21" s="47"/>
       <c r="J21" s="2"/>
     </row>
@@ -2033,18 +2033,18 @@
       <c r="D22" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="E22" s="66">
-        <v>6</v>
-      </c>
-      <c r="F22" s="67">
-        <v>10</v>
-      </c>
-      <c r="G22" s="68">
-        <v>27</v>
+      <c r="E22" s="62">
+        <v>42</v>
+      </c>
+      <c r="F22" s="63">
+        <v>80</v>
+      </c>
+      <c r="G22" s="64">
+        <v>243</v>
       </c>
       <c r="H22" s="47">
         <f t="shared" si="0"/>
-        <v>12.166666666666666</v>
+        <v>100.83333333333333</v>
       </c>
       <c r="J22" s="2"/>
     </row>
@@ -2057,18 +2057,18 @@
       <c r="D23" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="E23" s="66">
-        <v>3</v>
-      </c>
-      <c r="F23" s="67">
-        <v>5</v>
-      </c>
-      <c r="G23" s="68">
-        <v>14</v>
+      <c r="E23" s="62">
+        <v>21</v>
+      </c>
+      <c r="F23" s="63">
+        <v>40</v>
+      </c>
+      <c r="G23" s="64">
+        <v>126</v>
       </c>
       <c r="H23" s="47">
         <f t="shared" si="0"/>
-        <v>6.166666666666667</v>
+        <v>51.166666666666664</v>
       </c>
       <c r="J23" s="2"/>
     </row>
@@ -2081,18 +2081,18 @@
       <c r="D24" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="E24" s="66">
-        <v>2</v>
-      </c>
-      <c r="F24" s="67">
-        <v>3</v>
-      </c>
-      <c r="G24" s="68">
-        <v>9</v>
+      <c r="E24" s="62">
+        <v>14</v>
+      </c>
+      <c r="F24" s="63">
+        <v>24</v>
+      </c>
+      <c r="G24" s="64">
+        <v>81</v>
       </c>
       <c r="H24" s="47">
         <f t="shared" si="0"/>
-        <v>3.8333333333333335</v>
+        <v>31.833333333333332</v>
       </c>
       <c r="J24" s="2"/>
     </row>
@@ -2105,9 +2105,9 @@
       <c r="D25" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="E25" s="65"/>
-      <c r="F25" s="65"/>
-      <c r="G25" s="65"/>
+      <c r="E25" s="61"/>
+      <c r="F25" s="61"/>
+      <c r="G25" s="61"/>
       <c r="H25" s="47"/>
       <c r="J25" s="2"/>
     </row>
@@ -2120,18 +2120,18 @@
       <c r="D26" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="E26" s="66">
-        <v>6</v>
-      </c>
-      <c r="F26" s="67">
-        <v>10</v>
-      </c>
-      <c r="G26" s="68">
-        <v>27</v>
+      <c r="E26" s="62">
+        <v>42</v>
+      </c>
+      <c r="F26" s="63">
+        <v>80</v>
+      </c>
+      <c r="G26" s="64">
+        <v>243</v>
       </c>
       <c r="H26" s="47">
         <f t="shared" si="0"/>
-        <v>12.166666666666666</v>
+        <v>100.83333333333333</v>
       </c>
       <c r="J26" s="2"/>
     </row>
@@ -2144,18 +2144,18 @@
       <c r="D27" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="E27" s="66">
-        <v>8</v>
-      </c>
-      <c r="F27" s="67">
-        <v>14</v>
-      </c>
-      <c r="G27" s="68">
-        <v>36</v>
+      <c r="E27" s="62">
+        <v>56</v>
+      </c>
+      <c r="F27" s="63">
+        <v>112</v>
+      </c>
+      <c r="G27" s="64">
+        <v>324</v>
       </c>
       <c r="H27" s="47">
         <f t="shared" si="0"/>
-        <v>16.666666666666668</v>
+        <v>138</v>
       </c>
       <c r="J27" s="2"/>
     </row>
@@ -2168,18 +2168,18 @@
       <c r="D28" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="E28" s="66">
-        <v>6</v>
-      </c>
-      <c r="F28" s="67">
-        <v>10</v>
-      </c>
-      <c r="G28" s="68">
-        <v>27</v>
+      <c r="E28" s="62">
+        <v>42</v>
+      </c>
+      <c r="F28" s="63">
+        <v>80</v>
+      </c>
+      <c r="G28" s="64">
+        <v>243</v>
       </c>
       <c r="H28" s="47">
         <f t="shared" si="0"/>
-        <v>12.166666666666666</v>
+        <v>100.83333333333333</v>
       </c>
       <c r="J28" s="2"/>
     </row>
@@ -2192,9 +2192,9 @@
       <c r="D29" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="E29" s="65"/>
-      <c r="F29" s="65"/>
-      <c r="G29" s="65"/>
+      <c r="E29" s="61"/>
+      <c r="F29" s="61"/>
+      <c r="G29" s="61"/>
       <c r="H29" s="47"/>
       <c r="J29" s="2"/>
     </row>
@@ -2207,18 +2207,18 @@
       <c r="D30" s="22" t="s">
         <v>94</v>
       </c>
-      <c r="E30" s="69">
-        <v>12</v>
-      </c>
-      <c r="F30" s="70">
-        <v>20</v>
-      </c>
-      <c r="G30" s="71">
-        <v>54</v>
+      <c r="E30" s="65">
+        <v>84</v>
+      </c>
+      <c r="F30" s="66">
+        <v>160</v>
+      </c>
+      <c r="G30" s="67">
+        <v>486</v>
       </c>
       <c r="H30" s="47">
         <f t="shared" si="0"/>
-        <v>24.333333333333332</v>
+        <v>201.66666666666666</v>
       </c>
       <c r="J30" s="2"/>
     </row>
@@ -2231,9 +2231,9 @@
       <c r="D31" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="E31" s="65"/>
-      <c r="F31" s="65"/>
-      <c r="G31" s="65"/>
+      <c r="E31" s="61"/>
+      <c r="F31" s="61"/>
+      <c r="G31" s="61"/>
       <c r="H31" s="47"/>
       <c r="J31" s="2"/>
     </row>
@@ -2246,18 +2246,18 @@
       <c r="D32" s="25" t="s">
         <v>96</v>
       </c>
-      <c r="E32" s="72">
-        <v>4</v>
-      </c>
-      <c r="F32" s="73">
-        <v>7</v>
-      </c>
-      <c r="G32" s="71">
-        <v>18</v>
+      <c r="E32" s="68">
+        <v>28</v>
+      </c>
+      <c r="F32" s="69">
+        <v>56</v>
+      </c>
+      <c r="G32" s="67">
+        <v>162</v>
       </c>
       <c r="H32" s="47">
         <f t="shared" si="0"/>
-        <v>8.3333333333333339</v>
+        <v>69</v>
       </c>
       <c r="J32" s="2"/>
     </row>
@@ -2270,18 +2270,18 @@
       <c r="D33" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="E33" s="69">
-        <v>5</v>
-      </c>
-      <c r="F33" s="70">
-        <v>8</v>
-      </c>
-      <c r="G33" s="71">
-        <v>22</v>
+      <c r="E33" s="65">
+        <v>35</v>
+      </c>
+      <c r="F33" s="66">
+        <v>58</v>
+      </c>
+      <c r="G33" s="67">
+        <v>192</v>
       </c>
       <c r="H33" s="47">
         <f t="shared" si="0"/>
-        <v>9.8333333333333339</v>
+        <v>76.5</v>
       </c>
       <c r="J33" s="2"/>
     </row>
@@ -2294,9 +2294,9 @@
       <c r="D34" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="E34" s="65"/>
-      <c r="F34" s="65"/>
-      <c r="G34" s="65"/>
+      <c r="E34" s="61"/>
+      <c r="F34" s="61"/>
+      <c r="G34" s="61"/>
       <c r="H34" s="47"/>
       <c r="J34" s="2"/>
     </row>
@@ -2309,18 +2309,18 @@
       <c r="D35" s="21" t="s">
         <v>116</v>
       </c>
-      <c r="E35" s="69">
-        <v>4</v>
-      </c>
-      <c r="F35" s="70">
-        <v>7</v>
-      </c>
-      <c r="G35" s="71">
-        <v>18</v>
+      <c r="E35" s="65">
+        <v>28</v>
+      </c>
+      <c r="F35" s="66">
+        <v>56</v>
+      </c>
+      <c r="G35" s="67">
+        <v>162</v>
       </c>
       <c r="H35" s="47">
         <f t="shared" si="0"/>
-        <v>8.3333333333333339</v>
+        <v>69</v>
       </c>
       <c r="J35" s="2"/>
     </row>
@@ -2333,18 +2333,18 @@
       <c r="D36" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="E36" s="69">
-        <v>4</v>
-      </c>
-      <c r="F36" s="70">
-        <v>7</v>
-      </c>
-      <c r="G36" s="71">
-        <v>18</v>
+      <c r="E36" s="65">
+        <v>28</v>
+      </c>
+      <c r="F36" s="66">
+        <v>56</v>
+      </c>
+      <c r="G36" s="67">
+        <v>162</v>
       </c>
       <c r="H36" s="47">
         <f t="shared" si="0"/>
-        <v>8.3333333333333339</v>
+        <v>69</v>
       </c>
       <c r="J36" s="2"/>
     </row>
@@ -2357,9 +2357,9 @@
       <c r="D37" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="E37" s="65"/>
-      <c r="F37" s="65"/>
-      <c r="G37" s="65"/>
+      <c r="E37" s="61"/>
+      <c r="F37" s="61"/>
+      <c r="G37" s="61"/>
       <c r="H37" s="47"/>
       <c r="J37" s="2"/>
     </row>
@@ -2372,18 +2372,18 @@
       <c r="D38" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="E38" s="69">
-        <v>4</v>
-      </c>
-      <c r="F38" s="70">
-        <v>7</v>
-      </c>
-      <c r="G38" s="71">
-        <v>18</v>
+      <c r="E38" s="65">
+        <v>28</v>
+      </c>
+      <c r="F38" s="66">
+        <v>56</v>
+      </c>
+      <c r="G38" s="67">
+        <v>162</v>
       </c>
       <c r="H38" s="47">
         <f t="shared" si="0"/>
-        <v>8.3333333333333339</v>
+        <v>69</v>
       </c>
       <c r="J38" s="2"/>
     </row>
@@ -2396,18 +2396,18 @@
       <c r="D39" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="E39" s="69">
-        <v>2</v>
-      </c>
-      <c r="F39" s="70">
-        <v>3</v>
-      </c>
-      <c r="G39" s="71">
-        <v>9</v>
+      <c r="E39" s="65">
+        <v>14</v>
+      </c>
+      <c r="F39" s="66">
+        <v>24</v>
+      </c>
+      <c r="G39" s="67">
+        <v>81</v>
       </c>
       <c r="H39" s="47">
         <f t="shared" si="0"/>
-        <v>3.8333333333333335</v>
+        <v>31.833333333333332</v>
       </c>
       <c r="J39" s="2"/>
     </row>
@@ -2420,9 +2420,9 @@
       <c r="D40" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="E40" s="65"/>
-      <c r="F40" s="65"/>
-      <c r="G40" s="65"/>
+      <c r="E40" s="61"/>
+      <c r="F40" s="61"/>
+      <c r="G40" s="61"/>
       <c r="H40" s="47"/>
       <c r="J40" s="2"/>
     </row>
@@ -2435,18 +2435,18 @@
       <c r="D41" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="E41" s="69">
-        <v>5</v>
-      </c>
-      <c r="F41" s="70">
-        <v>8</v>
-      </c>
-      <c r="G41" s="71">
-        <v>22</v>
+      <c r="E41" s="65">
+        <v>35</v>
+      </c>
+      <c r="F41" s="66">
+        <v>64</v>
+      </c>
+      <c r="G41" s="67">
+        <v>198</v>
       </c>
       <c r="H41" s="47">
         <f t="shared" si="0"/>
-        <v>9.8333333333333339</v>
+        <v>81.5</v>
       </c>
       <c r="J41" s="2"/>
     </row>
@@ -2459,18 +2459,18 @@
       <c r="D42" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="E42" s="69">
-        <v>4</v>
-      </c>
-      <c r="F42" s="70">
-        <v>7</v>
-      </c>
-      <c r="G42" s="71">
-        <v>18</v>
+      <c r="E42" s="65">
+        <v>28</v>
+      </c>
+      <c r="F42" s="66">
+        <v>56</v>
+      </c>
+      <c r="G42" s="67">
+        <v>162</v>
       </c>
       <c r="H42" s="47">
         <f t="shared" si="0"/>
-        <v>8.3333333333333339</v>
+        <v>69</v>
       </c>
       <c r="J42" s="2"/>
     </row>
@@ -2483,9 +2483,9 @@
       <c r="D43" s="14" t="s">
         <v>112</v>
       </c>
-      <c r="E43" s="65"/>
-      <c r="F43" s="65"/>
-      <c r="G43" s="65"/>
+      <c r="E43" s="61"/>
+      <c r="F43" s="61"/>
+      <c r="G43" s="61"/>
       <c r="H43" s="47"/>
       <c r="J43" s="2"/>
     </row>
@@ -2498,18 +2498,18 @@
       <c r="D44" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="E44" s="69">
-        <v>6</v>
-      </c>
-      <c r="F44" s="70">
-        <v>10</v>
-      </c>
-      <c r="G44" s="71">
-        <v>27</v>
+      <c r="E44" s="65">
+        <v>42</v>
+      </c>
+      <c r="F44" s="66">
+        <v>80</v>
+      </c>
+      <c r="G44" s="67">
+        <v>243</v>
       </c>
       <c r="H44" s="47">
         <f t="shared" si="0"/>
-        <v>12.166666666666666</v>
+        <v>100.83333333333333</v>
       </c>
       <c r="J44" s="2"/>
     </row>
@@ -2522,18 +2522,18 @@
       <c r="D45" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="E45" s="69">
-        <v>5</v>
-      </c>
-      <c r="F45" s="70">
-        <v>8</v>
-      </c>
-      <c r="G45" s="71">
-        <v>22</v>
+      <c r="E45" s="65">
+        <v>35</v>
+      </c>
+      <c r="F45" s="66">
+        <v>64</v>
+      </c>
+      <c r="G45" s="67">
+        <v>198</v>
       </c>
       <c r="H45" s="47">
         <f t="shared" si="0"/>
-        <v>9.8333333333333339</v>
+        <v>81.5</v>
       </c>
       <c r="J45" s="2"/>
     </row>
@@ -2546,9 +2546,9 @@
       <c r="D46" s="14" t="s">
         <v>110</v>
       </c>
-      <c r="E46" s="65"/>
-      <c r="F46" s="65"/>
-      <c r="G46" s="65"/>
+      <c r="E46" s="61"/>
+      <c r="F46" s="61"/>
+      <c r="G46" s="61"/>
       <c r="H46" s="47"/>
       <c r="J46" s="2"/>
     </row>
@@ -2561,18 +2561,18 @@
       <c r="D47" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="E47" s="69">
-        <v>16</v>
-      </c>
-      <c r="F47" s="70">
-        <v>27</v>
-      </c>
-      <c r="G47" s="71">
-        <v>72</v>
+      <c r="E47" s="65">
+        <v>112</v>
+      </c>
+      <c r="F47" s="66">
+        <v>216</v>
+      </c>
+      <c r="G47" s="67">
+        <v>648</v>
       </c>
       <c r="H47" s="47">
         <f t="shared" si="0"/>
-        <v>32.666666666666664</v>
+        <v>270.66666666666669</v>
       </c>
       <c r="J47" s="2"/>
     </row>
@@ -2585,18 +2585,18 @@
       <c r="D48" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="E48" s="69">
-        <v>16</v>
-      </c>
-      <c r="F48" s="70">
-        <v>27</v>
-      </c>
-      <c r="G48" s="71">
-        <v>72</v>
+      <c r="E48" s="65">
+        <v>112</v>
+      </c>
+      <c r="F48" s="66">
+        <v>216</v>
+      </c>
+      <c r="G48" s="67">
+        <v>648</v>
       </c>
       <c r="H48" s="47">
         <f t="shared" si="0"/>
-        <v>32.666666666666664</v>
+        <v>270.66666666666669</v>
       </c>
       <c r="J48" s="2"/>
     </row>
@@ -2609,9 +2609,9 @@
       <c r="D49" s="14" t="s">
         <v>111</v>
       </c>
-      <c r="E49" s="65"/>
-      <c r="F49" s="65"/>
-      <c r="G49" s="65"/>
+      <c r="E49" s="61"/>
+      <c r="F49" s="61"/>
+      <c r="G49" s="61"/>
       <c r="H49" s="47"/>
       <c r="J49" s="2"/>
     </row>
@@ -2624,18 +2624,18 @@
       <c r="D50" s="21" t="s">
         <v>97</v>
       </c>
-      <c r="E50" s="69">
-        <v>4</v>
-      </c>
-      <c r="F50" s="70">
-        <v>7</v>
-      </c>
-      <c r="G50" s="71">
-        <v>18</v>
+      <c r="E50" s="65">
+        <v>28</v>
+      </c>
+      <c r="F50" s="66">
+        <v>56</v>
+      </c>
+      <c r="G50" s="67">
+        <v>162</v>
       </c>
       <c r="H50" s="47">
         <f t="shared" si="0"/>
-        <v>8.3333333333333339</v>
+        <v>69</v>
       </c>
       <c r="J50" s="2"/>
     </row>
@@ -2648,18 +2648,18 @@
       <c r="D51" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="E51" s="69">
-        <v>6</v>
-      </c>
-      <c r="F51" s="70">
-        <v>10</v>
-      </c>
-      <c r="G51" s="71">
-        <v>27</v>
+      <c r="E51" s="65">
+        <v>42</v>
+      </c>
+      <c r="F51" s="66">
+        <v>80</v>
+      </c>
+      <c r="G51" s="67">
+        <v>243</v>
       </c>
       <c r="H51" s="47">
         <f t="shared" si="0"/>
-        <v>12.166666666666666</v>
+        <v>100.83333333333333</v>
       </c>
       <c r="J51" s="2"/>
     </row>
@@ -2668,9 +2668,9 @@
       <c r="B52" s="16"/>
       <c r="C52" s="26"/>
       <c r="D52" s="27"/>
-      <c r="E52" s="74"/>
-      <c r="F52" s="75"/>
-      <c r="G52" s="76"/>
+      <c r="E52" s="70"/>
+      <c r="F52" s="71"/>
+      <c r="G52" s="72"/>
       <c r="H52" s="47"/>
       <c r="J52" s="2"/>
     </row>
@@ -2685,9 +2685,9 @@
       <c r="D53" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="E53" s="62"/>
-      <c r="F53" s="63"/>
-      <c r="G53" s="64"/>
+      <c r="E53" s="58"/>
+      <c r="F53" s="59"/>
+      <c r="G53" s="60"/>
       <c r="H53" s="47"/>
       <c r="J53" s="2"/>
     </row>
@@ -2700,18 +2700,18 @@
       <c r="D54" s="21" t="s">
         <v>98</v>
       </c>
-      <c r="E54" s="69">
-        <v>6</v>
-      </c>
-      <c r="F54" s="70">
-        <v>10</v>
-      </c>
-      <c r="G54" s="71">
-        <v>27</v>
+      <c r="E54" s="65">
+        <v>42</v>
+      </c>
+      <c r="F54" s="66">
+        <v>80</v>
+      </c>
+      <c r="G54" s="67">
+        <v>243</v>
       </c>
       <c r="H54" s="47">
         <f t="shared" si="0"/>
-        <v>12.166666666666666</v>
+        <v>100.83333333333333</v>
       </c>
       <c r="J54" s="2"/>
     </row>
@@ -2724,18 +2724,18 @@
       <c r="D55" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="E55" s="69">
-        <v>5</v>
-      </c>
-      <c r="F55" s="70">
-        <v>8</v>
-      </c>
-      <c r="G55" s="71">
-        <v>22</v>
+      <c r="E55" s="65">
+        <v>35</v>
+      </c>
+      <c r="F55" s="66">
+        <v>64</v>
+      </c>
+      <c r="G55" s="67">
+        <v>198</v>
       </c>
       <c r="H55" s="47">
         <f t="shared" si="0"/>
-        <v>9.8333333333333339</v>
+        <v>81.5</v>
       </c>
       <c r="J55" s="2"/>
     </row>
@@ -2748,18 +2748,18 @@
       <c r="D56" s="21" t="s">
         <v>99</v>
       </c>
-      <c r="E56" s="69">
-        <v>3</v>
-      </c>
-      <c r="F56" s="70">
-        <v>5</v>
-      </c>
-      <c r="G56" s="71">
-        <v>14</v>
+      <c r="E56" s="65">
+        <v>21</v>
+      </c>
+      <c r="F56" s="66">
+        <v>40</v>
+      </c>
+      <c r="G56" s="67">
+        <v>126</v>
       </c>
       <c r="H56" s="47">
         <f t="shared" si="0"/>
-        <v>6.166666666666667</v>
+        <v>51.166666666666664</v>
       </c>
       <c r="J56" s="2"/>
     </row>
@@ -2772,18 +2772,18 @@
       <c r="D57" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="E57" s="69">
-        <v>4</v>
-      </c>
-      <c r="F57" s="70">
-        <v>7</v>
-      </c>
-      <c r="G57" s="71">
-        <v>18</v>
+      <c r="E57" s="65">
+        <v>28</v>
+      </c>
+      <c r="F57" s="66">
+        <v>56</v>
+      </c>
+      <c r="G57" s="67">
+        <v>162</v>
       </c>
       <c r="H57" s="47">
         <f t="shared" si="0"/>
-        <v>8.3333333333333339</v>
+        <v>69</v>
       </c>
       <c r="J57" s="2"/>
     </row>
@@ -2796,18 +2796,18 @@
       <c r="D58" s="21" t="s">
         <v>100</v>
       </c>
-      <c r="E58" s="69">
-        <v>3</v>
-      </c>
-      <c r="F58" s="70">
-        <v>5</v>
-      </c>
-      <c r="G58" s="71">
-        <v>14</v>
+      <c r="E58" s="65">
+        <v>21</v>
+      </c>
+      <c r="F58" s="66">
+        <v>40</v>
+      </c>
+      <c r="G58" s="67">
+        <v>126</v>
       </c>
       <c r="H58" s="47">
         <f t="shared" si="0"/>
-        <v>6.166666666666667</v>
+        <v>51.166666666666664</v>
       </c>
       <c r="J58" s="2"/>
     </row>
@@ -2816,9 +2816,9 @@
       <c r="B59" s="16"/>
       <c r="C59" s="51"/>
       <c r="D59" s="27"/>
-      <c r="E59" s="74"/>
-      <c r="F59" s="75"/>
-      <c r="G59" s="76"/>
+      <c r="E59" s="70"/>
+      <c r="F59" s="71"/>
+      <c r="G59" s="72"/>
       <c r="H59" s="47"/>
       <c r="J59" s="2"/>
     </row>
@@ -2831,9 +2831,9 @@
       <c r="D60" s="32" t="s">
         <v>86</v>
       </c>
-      <c r="E60" s="62"/>
-      <c r="F60" s="63"/>
-      <c r="G60" s="64"/>
+      <c r="E60" s="58"/>
+      <c r="F60" s="59"/>
+      <c r="G60" s="60"/>
       <c r="H60" s="47"/>
       <c r="J60" s="2"/>
     </row>
@@ -2846,18 +2846,18 @@
       <c r="D61" s="21" t="s">
         <v>113</v>
       </c>
-      <c r="E61" s="69">
-        <v>5</v>
-      </c>
-      <c r="F61" s="70">
-        <v>8</v>
-      </c>
-      <c r="G61" s="71">
-        <v>22</v>
+      <c r="E61" s="65">
+        <v>35</v>
+      </c>
+      <c r="F61" s="66">
+        <v>64</v>
+      </c>
+      <c r="G61" s="67">
+        <v>198</v>
       </c>
       <c r="H61" s="47">
         <f t="shared" si="0"/>
-        <v>9.8333333333333339</v>
+        <v>81.5</v>
       </c>
       <c r="J61" s="2"/>
     </row>
@@ -2870,18 +2870,18 @@
       <c r="D62" s="21" t="s">
         <v>114</v>
       </c>
-      <c r="E62" s="69">
-        <v>3</v>
-      </c>
-      <c r="F62" s="70">
-        <v>5</v>
-      </c>
-      <c r="G62" s="71">
-        <v>14</v>
+      <c r="E62" s="65">
+        <v>21</v>
+      </c>
+      <c r="F62" s="66">
+        <v>40</v>
+      </c>
+      <c r="G62" s="67">
+        <v>126</v>
       </c>
       <c r="H62" s="47">
         <f t="shared" si="0"/>
-        <v>6.166666666666667</v>
+        <v>51.166666666666664</v>
       </c>
       <c r="J62" s="2"/>
     </row>
@@ -2894,18 +2894,18 @@
       <c r="D63" s="21" t="s">
         <v>101</v>
       </c>
-      <c r="E63" s="69">
-        <v>6</v>
-      </c>
-      <c r="F63" s="70">
-        <v>10</v>
-      </c>
-      <c r="G63" s="71">
-        <v>27</v>
+      <c r="E63" s="65">
+        <v>42</v>
+      </c>
+      <c r="F63" s="66">
+        <v>80</v>
+      </c>
+      <c r="G63" s="67">
+        <v>243</v>
       </c>
       <c r="H63" s="47">
         <f t="shared" si="0"/>
-        <v>12.166666666666666</v>
+        <v>100.83333333333333</v>
       </c>
       <c r="J63" s="2"/>
     </row>
@@ -2918,18 +2918,18 @@
       <c r="D64" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="E64" s="69">
-        <v>4</v>
-      </c>
-      <c r="F64" s="70">
-        <v>7</v>
-      </c>
-      <c r="G64" s="71">
-        <v>18</v>
+      <c r="E64" s="65">
+        <v>28</v>
+      </c>
+      <c r="F64" s="66">
+        <v>56</v>
+      </c>
+      <c r="G64" s="67">
+        <v>162</v>
       </c>
       <c r="H64" s="47">
         <f t="shared" si="0"/>
-        <v>8.3333333333333339</v>
+        <v>69</v>
       </c>
       <c r="J64" s="2"/>
     </row>
@@ -2938,9 +2938,9 @@
       <c r="B65" s="16"/>
       <c r="C65" s="51"/>
       <c r="D65" s="27"/>
-      <c r="E65" s="74"/>
-      <c r="F65" s="75"/>
-      <c r="G65" s="76"/>
+      <c r="E65" s="70"/>
+      <c r="F65" s="71"/>
+      <c r="G65" s="72"/>
       <c r="H65" s="47"/>
       <c r="J65" s="2"/>
     </row>
@@ -2953,9 +2953,9 @@
       <c r="D66" s="32" t="s">
         <v>87</v>
       </c>
-      <c r="E66" s="77"/>
-      <c r="F66" s="78"/>
-      <c r="G66" s="79"/>
+      <c r="E66" s="73"/>
+      <c r="F66" s="74"/>
+      <c r="G66" s="75"/>
       <c r="H66" s="47"/>
       <c r="J66" s="2"/>
     </row>
@@ -2968,18 +2968,18 @@
       <c r="D67" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="E67" s="69">
-        <v>4</v>
-      </c>
-      <c r="F67" s="70">
-        <v>7</v>
-      </c>
-      <c r="G67" s="80">
-        <v>18</v>
+      <c r="E67" s="65">
+        <v>28</v>
+      </c>
+      <c r="F67" s="66">
+        <v>56</v>
+      </c>
+      <c r="G67" s="76">
+        <v>168</v>
       </c>
       <c r="H67" s="47">
         <f t="shared" si="0"/>
-        <v>8.3333333333333339</v>
+        <v>70</v>
       </c>
       <c r="J67" s="2"/>
     </row>
@@ -2992,18 +2992,18 @@
       <c r="D68" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="E68" s="69">
-        <v>3</v>
-      </c>
-      <c r="F68" s="70">
-        <v>5</v>
-      </c>
-      <c r="G68" s="80">
-        <v>14</v>
+      <c r="E68" s="65">
+        <v>21</v>
+      </c>
+      <c r="F68" s="66">
+        <v>40</v>
+      </c>
+      <c r="G68" s="76">
+        <v>126</v>
       </c>
       <c r="H68" s="47">
         <f t="shared" si="0"/>
-        <v>6.166666666666667</v>
+        <v>51.166666666666664</v>
       </c>
       <c r="J68" s="2"/>
     </row>
@@ -3016,18 +3016,18 @@
       <c r="D69" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="E69" s="69">
-        <v>2</v>
-      </c>
-      <c r="F69" s="70">
-        <v>3</v>
-      </c>
-      <c r="G69" s="80">
-        <v>9</v>
+      <c r="E69" s="65">
+        <v>14</v>
+      </c>
+      <c r="F69" s="66">
+        <v>24</v>
+      </c>
+      <c r="G69" s="76">
+        <v>81</v>
       </c>
       <c r="H69" s="47">
         <f t="shared" si="0"/>
-        <v>3.8333333333333335</v>
+        <v>31.833333333333332</v>
       </c>
       <c r="J69" s="2"/>
     </row>
@@ -3036,9 +3036,9 @@
       <c r="B70" s="33"/>
       <c r="C70" s="53"/>
       <c r="D70" s="22"/>
-      <c r="E70" s="74"/>
-      <c r="F70" s="75"/>
-      <c r="G70" s="76"/>
+      <c r="E70" s="70"/>
+      <c r="F70" s="71"/>
+      <c r="G70" s="72"/>
       <c r="H70" s="47"/>
       <c r="J70" s="2"/>
     </row>
@@ -3051,9 +3051,9 @@
       <c r="D71" s="32" t="s">
         <v>88</v>
       </c>
-      <c r="E71" s="62"/>
-      <c r="F71" s="63"/>
-      <c r="G71" s="64"/>
+      <c r="E71" s="58"/>
+      <c r="F71" s="59"/>
+      <c r="G71" s="60"/>
       <c r="H71" s="47"/>
       <c r="J71" s="2"/>
     </row>
@@ -3066,18 +3066,18 @@
       <c r="D72" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="E72" s="69">
-        <v>3</v>
-      </c>
-      <c r="F72" s="70">
-        <v>5</v>
-      </c>
-      <c r="G72" s="71">
-        <v>14</v>
+      <c r="E72" s="65">
+        <v>21</v>
+      </c>
+      <c r="F72" s="66">
+        <v>40</v>
+      </c>
+      <c r="G72" s="67">
+        <v>126</v>
       </c>
       <c r="H72" s="47">
         <f t="shared" si="0"/>
-        <v>6.166666666666667</v>
+        <v>51.166666666666664</v>
       </c>
       <c r="J72" s="2"/>
     </row>
@@ -3090,18 +3090,18 @@
       <c r="D73" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="E73" s="69">
-        <v>4</v>
-      </c>
-      <c r="F73" s="70">
-        <v>7</v>
-      </c>
-      <c r="G73" s="71">
-        <v>18</v>
+      <c r="E73" s="65">
+        <v>28</v>
+      </c>
+      <c r="F73" s="66">
+        <v>56</v>
+      </c>
+      <c r="G73" s="67">
+        <v>162</v>
       </c>
       <c r="H73" s="47">
         <f t="shared" si="0"/>
-        <v>8.3333333333333339</v>
+        <v>69</v>
       </c>
       <c r="J73" s="2"/>
     </row>
@@ -3114,18 +3114,18 @@
       <c r="D74" s="25" t="s">
         <v>49</v>
       </c>
-      <c r="E74" s="72">
-        <v>6</v>
-      </c>
-      <c r="F74" s="73">
-        <v>10</v>
-      </c>
-      <c r="G74" s="81">
-        <v>27</v>
+      <c r="E74" s="68">
+        <v>42</v>
+      </c>
+      <c r="F74" s="69">
+        <v>80</v>
+      </c>
+      <c r="G74" s="77">
+        <v>243</v>
       </c>
       <c r="H74" s="47">
         <f t="shared" si="0"/>
-        <v>12.166666666666666</v>
+        <v>100.83333333333333</v>
       </c>
       <c r="J74" s="2"/>
     </row>
@@ -3138,18 +3138,18 @@
       <c r="D75" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="E75" s="69">
-        <v>2</v>
-      </c>
-      <c r="F75" s="70">
-        <v>3</v>
-      </c>
-      <c r="G75" s="71">
-        <v>9</v>
+      <c r="E75" s="65">
+        <v>14</v>
+      </c>
+      <c r="F75" s="66">
+        <v>24</v>
+      </c>
+      <c r="G75" s="67">
+        <v>81</v>
       </c>
       <c r="H75" s="47">
         <f t="shared" si="0"/>
-        <v>3.8333333333333335</v>
+        <v>31.833333333333332</v>
       </c>
       <c r="J75" s="2"/>
     </row>
@@ -3158,9 +3158,9 @@
       <c r="B76" s="33"/>
       <c r="C76" s="53"/>
       <c r="D76" s="22"/>
-      <c r="E76" s="74"/>
-      <c r="F76" s="75"/>
-      <c r="G76" s="76"/>
+      <c r="E76" s="70"/>
+      <c r="F76" s="71"/>
+      <c r="G76" s="72"/>
       <c r="H76" s="47"/>
       <c r="J76" s="2"/>
     </row>
@@ -3173,9 +3173,9 @@
       <c r="D77" s="36" t="s">
         <v>89</v>
       </c>
-      <c r="E77" s="62"/>
-      <c r="F77" s="63"/>
-      <c r="G77" s="64"/>
+      <c r="E77" s="58"/>
+      <c r="F77" s="59"/>
+      <c r="G77" s="60"/>
       <c r="H77" s="47"/>
       <c r="J77" s="2"/>
     </row>
@@ -3188,18 +3188,18 @@
       <c r="D78" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="E78" s="69">
-        <v>2</v>
-      </c>
-      <c r="F78" s="70">
-        <v>3</v>
-      </c>
-      <c r="G78" s="71">
-        <v>9</v>
+      <c r="E78" s="65">
+        <v>14</v>
+      </c>
+      <c r="F78" s="66">
+        <v>24</v>
+      </c>
+      <c r="G78" s="67">
+        <v>81</v>
       </c>
       <c r="H78" s="47">
         <f t="shared" ref="H78:H88" si="1">(E78 + 4*F78 + G78)/6</f>
-        <v>3.8333333333333335</v>
+        <v>31.833333333333332</v>
       </c>
       <c r="J78" s="2"/>
     </row>
@@ -3212,18 +3212,18 @@
       <c r="D79" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="E79" s="69">
-        <v>12</v>
-      </c>
-      <c r="F79" s="70">
-        <v>20</v>
-      </c>
-      <c r="G79" s="71">
-        <v>54</v>
+      <c r="E79" s="65">
+        <v>84</v>
+      </c>
+      <c r="F79" s="66">
+        <v>160</v>
+      </c>
+      <c r="G79" s="67">
+        <v>486</v>
       </c>
       <c r="H79" s="47">
         <f t="shared" si="1"/>
-        <v>24.333333333333332</v>
+        <v>201.66666666666666</v>
       </c>
       <c r="J79" s="2"/>
     </row>
@@ -3236,18 +3236,18 @@
       <c r="D80" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="E80" s="69">
-        <v>3</v>
-      </c>
-      <c r="F80" s="70">
-        <v>5</v>
-      </c>
-      <c r="G80" s="71">
-        <v>14</v>
+      <c r="E80" s="65">
+        <v>21</v>
+      </c>
+      <c r="F80" s="66">
+        <v>40</v>
+      </c>
+      <c r="G80" s="67">
+        <v>126</v>
       </c>
       <c r="H80" s="47">
         <f t="shared" si="1"/>
-        <v>6.166666666666667</v>
+        <v>51.166666666666664</v>
       </c>
       <c r="J80" s="2"/>
     </row>
@@ -3260,18 +3260,18 @@
       <c r="D81" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="E81" s="69">
-        <v>3</v>
-      </c>
-      <c r="F81" s="70">
-        <v>5</v>
-      </c>
-      <c r="G81" s="71">
-        <v>14</v>
+      <c r="E81" s="65">
+        <v>21</v>
+      </c>
+      <c r="F81" s="66">
+        <v>40</v>
+      </c>
+      <c r="G81" s="67">
+        <v>126</v>
       </c>
       <c r="H81" s="47">
         <f t="shared" si="1"/>
-        <v>6.166666666666667</v>
+        <v>51.166666666666664</v>
       </c>
       <c r="J81" s="2"/>
     </row>
@@ -3284,18 +3284,18 @@
       <c r="D82" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="E82" s="69">
-        <v>6</v>
-      </c>
-      <c r="F82" s="70">
-        <v>10</v>
-      </c>
-      <c r="G82" s="71">
-        <v>27</v>
+      <c r="E82" s="65">
+        <v>42</v>
+      </c>
+      <c r="F82" s="66">
+        <v>80</v>
+      </c>
+      <c r="G82" s="67">
+        <v>243</v>
       </c>
       <c r="H82" s="47">
         <f t="shared" si="1"/>
-        <v>12.166666666666666</v>
+        <v>100.83333333333333</v>
       </c>
       <c r="J82" s="2"/>
     </row>
@@ -3304,9 +3304,9 @@
       <c r="B83" s="33"/>
       <c r="C83" s="53"/>
       <c r="D83" s="22"/>
-      <c r="E83" s="74"/>
-      <c r="F83" s="75"/>
-      <c r="G83" s="76"/>
+      <c r="E83" s="70"/>
+      <c r="F83" s="71"/>
+      <c r="G83" s="72"/>
       <c r="H83" s="47"/>
       <c r="J83" s="2"/>
     </row>
@@ -3319,9 +3319,9 @@
       <c r="D84" s="36" t="s">
         <v>90</v>
       </c>
-      <c r="E84" s="62"/>
-      <c r="F84" s="63"/>
-      <c r="G84" s="64"/>
+      <c r="E84" s="58"/>
+      <c r="F84" s="59"/>
+      <c r="G84" s="60"/>
       <c r="H84" s="47"/>
       <c r="J84" s="2"/>
     </row>
@@ -3334,18 +3334,18 @@
       <c r="D85" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="E85" s="69">
-        <v>6</v>
-      </c>
-      <c r="F85" s="70">
-        <v>10</v>
-      </c>
-      <c r="G85" s="71">
-        <v>27</v>
+      <c r="E85" s="65">
+        <v>42</v>
+      </c>
+      <c r="F85" s="66">
+        <v>80</v>
+      </c>
+      <c r="G85" s="67">
+        <v>243</v>
       </c>
       <c r="H85" s="47">
         <f t="shared" si="1"/>
-        <v>12.166666666666666</v>
+        <v>100.83333333333333</v>
       </c>
       <c r="J85" s="2"/>
     </row>
@@ -3358,18 +3358,18 @@
       <c r="D86" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="E86" s="69">
-        <v>8</v>
-      </c>
-      <c r="F86" s="70">
-        <v>14</v>
-      </c>
-      <c r="G86" s="71">
-        <v>36</v>
+      <c r="E86" s="65">
+        <v>56</v>
+      </c>
+      <c r="F86" s="66">
+        <v>122</v>
+      </c>
+      <c r="G86" s="67">
+        <v>324</v>
       </c>
       <c r="H86" s="47">
         <f t="shared" si="1"/>
-        <v>16.666666666666668</v>
+        <v>144.66666666666666</v>
       </c>
       <c r="J86" s="2"/>
     </row>
@@ -3382,18 +3382,18 @@
       <c r="D87" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="E87" s="69">
-        <v>10</v>
-      </c>
-      <c r="F87" s="70">
-        <v>17</v>
-      </c>
-      <c r="G87" s="71">
-        <v>45</v>
+      <c r="E87" s="65">
+        <v>70</v>
+      </c>
+      <c r="F87" s="66">
+        <v>136</v>
+      </c>
+      <c r="G87" s="67">
+        <v>405</v>
       </c>
       <c r="H87" s="47">
         <f t="shared" si="1"/>
-        <v>20.5</v>
+        <v>169.83333333333334</v>
       </c>
       <c r="J87" s="2"/>
     </row>
@@ -3406,18 +3406,18 @@
       <c r="D88" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="E88" s="69">
-        <v>6</v>
-      </c>
-      <c r="F88" s="70">
-        <v>10</v>
-      </c>
-      <c r="G88" s="71">
-        <v>27</v>
+      <c r="E88" s="65">
+        <v>42</v>
+      </c>
+      <c r="F88" s="66">
+        <v>80</v>
+      </c>
+      <c r="G88" s="67">
+        <v>243</v>
       </c>
       <c r="H88" s="47">
         <f t="shared" si="1"/>
-        <v>12.166666666666666</v>
+        <v>100.83333333333333</v>
       </c>
       <c r="J88" s="2"/>
     </row>
@@ -3440,19 +3440,19 @@
       <c r="D90" s="29"/>
       <c r="E90" s="40">
         <f>SUM(E11:E88)</f>
-        <v>293</v>
+        <v>2051</v>
       </c>
       <c r="F90" s="40">
         <f t="shared" ref="F90:G90" si="2">SUM(F11:F88)</f>
-        <v>492</v>
+        <v>3940</v>
       </c>
       <c r="G90" s="40">
         <f t="shared" si="2"/>
-        <v>1321</v>
+        <v>11889</v>
       </c>
       <c r="H90" s="40">
         <f>SUM(H11:H88)</f>
-        <v>596.99999999999989</v>
+        <v>4950</v>
       </c>
       <c r="J90" s="2"/>
     </row>
